--- a/themes/smsNotifications.xlsx
+++ b/themes/smsNotifications.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -450,121 +450,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          • Со второго месяца — 129 рублей в месяц. Комиссия списывается каждый месяц в день подключения услуги — это предоплата за следующий месяц</t>
+          <t xml:space="preserve">    В течение первого месяца - без комиссии.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">          • Со второго месяца — 129 рублей в месяц. Комиссия списывается каждый месяц в день подключения услуги — это предоплата за следующий месяц.</t>
+          <t xml:space="preserve">    В течение первого месяца — без комиссии.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Со второго месяца — 129 рублей в месяц. Комиссия за предоставление услуги списывается ежемесячно в дату подключения услуги путем предоплаты за последующий месяц</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      • Со второго месяца — 129 рублей в месяц. Комиссия за предоставление услуги списывается ежемесячно в дату подключения услуги путем предоплаты за последующий месяц.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>22</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - "Стоимость услуги «Сервис уведомлений» составляет {{$temp.rubleForm}}"</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - "Стоимость услуги «Сервис уведомлений» составляет {{$temp.rubleForm}}."</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения (внутри кавычек)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    В течение первого месяца - без комиссии.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    В течение первого месяца — без комиссии.</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>дефис заменён на тире</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>46</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     3. По номеру горячей линии — 8-800-250-57-57</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     3. По номеру горячей линии — 8-800-250-57-57.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения — для единообразия с аналогичной фразой выше по файлу (стр. 40), где точка есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      3. В [банкомате Уралсиба]({{$temp.ATMLink}})</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      3. В [банкомате Уралсиба]({{$temp.ATMLink}}).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка — для единообразия с соседними пунктами списка (стр. 85, 86, 88), где точка есть</t>
         </is>
       </c>
     </row>
